--- a/患者批量导入模板.xlsx
+++ b/患者批量导入模板.xlsx
@@ -570,17 +570,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>选填，多个用逗号分隔</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选填，多个用逗号分隔</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -652,13 +652,13 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>湿性AMD</t>
+          <t>湿性AMD,糖尿病视网膜病变</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>雷珠单抗</t>
+          <t>雷珠单抗,康柏西普</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>

--- a/患者批量导入模板.xlsx
+++ b/患者批量导入模板.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
@@ -463,6 +463,7 @@
     <col customWidth="1" max="14" min="14" width="12"/>
     <col customWidth="1" max="15" min="15" width="12"/>
     <col customWidth="1" max="16" min="16" width="12"/>
+    <col customWidth="1" max="17" min="17" width="20"/>
   </cols>
   <sheetData>
     <row customHeight="1" ht="25" r="1">
@@ -546,6 +547,11 @@
           <t>已完成针数</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row customHeight="1" ht="20" r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -628,6 +634,11 @@
           <t>选填，仅经治患者填写</t>
         </is>
       </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -698,6 +709,11 @@
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>这是备注信息</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
